--- a/zara周报数据源/热词部分/0428-0504热词/家居.xlsx
+++ b/zara周报数据源/热词部分/0428-0504热词/家居.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:N8">
-  <autoFilter ref="A3:N8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:N13">
+  <autoFilter ref="A3:N13"/>
   <tableColumns count="14">
     <tableColumn id="1" name="家居热词分类"/>
     <tableColumn id="2" name="上架天数"/>
@@ -450,8 +450,6 @@
     <row r="1">
       <c t="str">
         <v>应用的筛选器: 
-搜索PV 大于 20
-hotword_audiocontent.1 不等于 毛巾、连体衣、连衣裙、显瘦牛仔裤、挂钩、衬衫合集 或 
 category 等于 家居
 Date 在 2026/4/28 当天或之后 和 在 2026/5/5 之前
 Search Entrance 等于 热词搜索
@@ -729,6 +727,226 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c t="str">
+        <v>玻璃杯</v>
+      </c>
+      <c s="6">
+        <v>7</v>
+      </c>
+      <c s="7">
+        <v>20</v>
+      </c>
+      <c s="8">
+        <v>16</v>
+      </c>
+      <c s="9">
+        <v>1.25</v>
+      </c>
+      <c s="10">
+        <v>2</v>
+      </c>
+      <c s="11">
+        <v>2</v>
+      </c>
+      <c s="12">
+        <v>0.125</v>
+      </c>
+      <c s="13">
+        <v/>
+      </c>
+      <c s="14">
+        <v/>
+      </c>
+      <c s="15">
+        <v/>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c t="str">
+        <v>马克杯</v>
+      </c>
+      <c s="6">
+        <v>7</v>
+      </c>
+      <c s="7">
+        <v>19</v>
+      </c>
+      <c s="8">
+        <v>18</v>
+      </c>
+      <c s="9">
+        <v>1.05555555555556</v>
+      </c>
+      <c s="10">
+        <v>5</v>
+      </c>
+      <c s="11">
+        <v>2</v>
+      </c>
+      <c s="12">
+        <v>0.111111111111111</v>
+      </c>
+      <c s="13">
+        <v/>
+      </c>
+      <c s="14">
+        <v/>
+      </c>
+      <c s="15">
+        <v/>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c t="str">
+        <v>迷你小盘</v>
+      </c>
+      <c s="6">
+        <v>3</v>
+      </c>
+      <c s="7">
+        <v>14</v>
+      </c>
+      <c s="8">
+        <v>9</v>
+      </c>
+      <c s="9">
+        <v>1.55555555555556</v>
+      </c>
+      <c s="10">
+        <v>4</v>
+      </c>
+      <c s="11">
+        <v>2</v>
+      </c>
+      <c s="12">
+        <v>0.222222222222222</v>
+      </c>
+      <c s="13">
+        <v>2</v>
+      </c>
+      <c s="14">
+        <v>2</v>
+      </c>
+      <c s="15">
+        <v>0.222222222222222</v>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c t="str">
+        <v>盘子</v>
+      </c>
+      <c s="6">
+        <v>4</v>
+      </c>
+      <c s="7">
+        <v>14</v>
+      </c>
+      <c s="8">
+        <v>7</v>
+      </c>
+      <c s="9">
+        <v>2</v>
+      </c>
+      <c s="10">
+        <v>10</v>
+      </c>
+      <c s="11">
+        <v>4</v>
+      </c>
+      <c s="12">
+        <v>0.571428571428571</v>
+      </c>
+      <c s="13">
+        <v>2</v>
+      </c>
+      <c s="14">
+        <v>1</v>
+      </c>
+      <c s="15">
+        <v>0.142857142857143</v>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c t="str">
+        <v>毛绒玩具</v>
+      </c>
+      <c s="6">
+        <v>7</v>
+      </c>
+      <c s="7">
+        <v>12</v>
+      </c>
+      <c s="8">
+        <v>12</v>
+      </c>
+      <c s="9">
+        <v>1</v>
+      </c>
+      <c s="10">
+        <v/>
+      </c>
+      <c s="11">
+        <v/>
+      </c>
+      <c s="12">
+        <v/>
+      </c>
+      <c s="13">
+        <v/>
+      </c>
+      <c s="14">
+        <v/>
+      </c>
+      <c s="15">
+        <v/>
+      </c>
+      <c s="16">
+        <v/>
+      </c>
+      <c s="17">
+        <v/>
+      </c>
+      <c s="18">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/zara周报数据源/热词部分/0428-0504热词/家居.xlsx
+++ b/zara周报数据源/热词部分/0428-0504热词/家居.xlsx
@@ -125,8 +125,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:N13">
-  <autoFilter ref="A3:N13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:N8">
+  <autoFilter ref="A3:N8"/>
   <tableColumns count="14">
     <tableColumn id="1" name="家居热词分类"/>
     <tableColumn id="2" name="上架天数"/>
@@ -450,6 +450,8 @@
     <row r="1">
       <c t="str">
         <v>应用的筛选器: 
+搜索PV 大于 20
+hotword_audiocontent.1 不等于 毛巾、连体衣、连衣裙、显瘦牛仔裤、挂钩、衬衫合集 或 
 category 等于 家居
 Date 在 2026/4/28 当天或之后 和 在 2026/5/5 之前
 Search Entrance 等于 热词搜索
@@ -727,226 +729,6 @@
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c t="str">
-        <v>玻璃杯</v>
-      </c>
-      <c s="6">
-        <v>7</v>
-      </c>
-      <c s="7">
-        <v>20</v>
-      </c>
-      <c s="8">
-        <v>16</v>
-      </c>
-      <c s="9">
-        <v>1.25</v>
-      </c>
-      <c s="10">
-        <v>2</v>
-      </c>
-      <c s="11">
-        <v>2</v>
-      </c>
-      <c s="12">
-        <v>0.125</v>
-      </c>
-      <c s="13">
-        <v/>
-      </c>
-      <c s="14">
-        <v/>
-      </c>
-      <c s="15">
-        <v/>
-      </c>
-      <c s="16">
-        <v/>
-      </c>
-      <c s="17">
-        <v/>
-      </c>
-      <c s="18">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c t="str">
-        <v>马克杯</v>
-      </c>
-      <c s="6">
-        <v>7</v>
-      </c>
-      <c s="7">
-        <v>19</v>
-      </c>
-      <c s="8">
-        <v>18</v>
-      </c>
-      <c s="9">
-        <v>1.05555555555556</v>
-      </c>
-      <c s="10">
-        <v>5</v>
-      </c>
-      <c s="11">
-        <v>2</v>
-      </c>
-      <c s="12">
-        <v>0.111111111111111</v>
-      </c>
-      <c s="13">
-        <v/>
-      </c>
-      <c s="14">
-        <v/>
-      </c>
-      <c s="15">
-        <v/>
-      </c>
-      <c s="16">
-        <v/>
-      </c>
-      <c s="17">
-        <v/>
-      </c>
-      <c s="18">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c t="str">
-        <v>迷你小盘</v>
-      </c>
-      <c s="6">
-        <v>3</v>
-      </c>
-      <c s="7">
-        <v>14</v>
-      </c>
-      <c s="8">
-        <v>9</v>
-      </c>
-      <c s="9">
-        <v>1.55555555555556</v>
-      </c>
-      <c s="10">
-        <v>4</v>
-      </c>
-      <c s="11">
-        <v>2</v>
-      </c>
-      <c s="12">
-        <v>0.222222222222222</v>
-      </c>
-      <c s="13">
-        <v>2</v>
-      </c>
-      <c s="14">
-        <v>2</v>
-      </c>
-      <c s="15">
-        <v>0.222222222222222</v>
-      </c>
-      <c s="16">
-        <v/>
-      </c>
-      <c s="17">
-        <v/>
-      </c>
-      <c s="18">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c t="str">
-        <v>盘子</v>
-      </c>
-      <c s="6">
-        <v>4</v>
-      </c>
-      <c s="7">
-        <v>14</v>
-      </c>
-      <c s="8">
-        <v>7</v>
-      </c>
-      <c s="9">
-        <v>2</v>
-      </c>
-      <c s="10">
-        <v>10</v>
-      </c>
-      <c s="11">
-        <v>4</v>
-      </c>
-      <c s="12">
-        <v>0.571428571428571</v>
-      </c>
-      <c s="13">
-        <v>2</v>
-      </c>
-      <c s="14">
-        <v>1</v>
-      </c>
-      <c s="15">
-        <v>0.142857142857143</v>
-      </c>
-      <c s="16">
-        <v/>
-      </c>
-      <c s="17">
-        <v/>
-      </c>
-      <c s="18">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c t="str">
-        <v>毛绒玩具</v>
-      </c>
-      <c s="6">
-        <v>7</v>
-      </c>
-      <c s="7">
-        <v>12</v>
-      </c>
-      <c s="8">
-        <v>12</v>
-      </c>
-      <c s="9">
-        <v>1</v>
-      </c>
-      <c s="10">
-        <v/>
-      </c>
-      <c s="11">
-        <v/>
-      </c>
-      <c s="12">
-        <v/>
-      </c>
-      <c s="13">
-        <v/>
-      </c>
-      <c s="14">
-        <v/>
-      </c>
-      <c s="15">
-        <v/>
-      </c>
-      <c s="16">
-        <v/>
-      </c>
-      <c s="17">
-        <v/>
-      </c>
-      <c s="18">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
